--- a/pages/ParaFactorTool/Para_results.xlsx
+++ b/pages/ParaFactorTool/Para_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B658A42A-D8E9-430C-B2B3-2A2853BD12D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A18D42F-55C8-42B6-ADDE-D0B582738A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{606A86C0-9597-4987-B511-48E10215E725}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{606A86C0-9597-4987-B511-48E10215E725}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="393">
   <si>
     <t>Athlete</t>
   </si>
@@ -1149,6 +1149,78 @@
   </si>
   <si>
     <t>RaceRank</t>
+  </si>
+  <si>
+    <t>HORDIES Maxime</t>
+  </si>
+  <si>
+    <t>CORNEGLIANI Fabrizio</t>
+  </si>
+  <si>
+    <t>WILCOX Barry</t>
+  </si>
+  <si>
+    <t>FERREIRA de MELO JUNIOR Marcos Ant.</t>
+  </si>
+  <si>
+    <t>JAHODA Patrik</t>
+  </si>
+  <si>
+    <t>FRUH Benjamin</t>
+  </si>
+  <si>
+    <t>BACHMAIER Ernst</t>
+  </si>
+  <si>
+    <t>SZCZEPANKIEWICZ Miroslaw</t>
+  </si>
+  <si>
+    <t>YANARUEDEE Phongchai</t>
+  </si>
+  <si>
+    <t>THA</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H12RR</t>
+  </si>
+  <si>
+    <t>JOUANNY Florian</t>
+  </si>
+  <si>
+    <t>GARROTE MUNOZ Sergio</t>
+  </si>
+  <si>
+    <t>MAZZONE Luca</t>
+  </si>
+  <si>
+    <t>WILLS Cody</t>
+  </si>
+  <si>
+    <t>MEAD Rory</t>
+  </si>
+  <si>
+    <t>SCHEICHL Manuel</t>
+  </si>
+  <si>
+    <t>KINNIE Matthew</t>
+  </si>
+  <si>
+    <t>HASDAI Amit</t>
+  </si>
+  <si>
+    <t>RIZZATO Omar</t>
+  </si>
+  <si>
+    <t>SCHMIED Yves</t>
+  </si>
+  <si>
+    <t>ISR</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1229,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm:ss.000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1194,13 +1266,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1516,7 +1587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD79A4C-9D7F-4A65-8AFE-5A6750D526F4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K452"/>
+  <dimension ref="A1:K471"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" customWidth="1"/>
@@ -1597,7 +1668,7 @@
       <c r="J2">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>38.4242098</v>
       </c>
     </row>
@@ -1632,7 +1703,7 @@
       <c r="J3">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
         <v>40.603696999999997</v>
       </c>
     </row>
@@ -1667,7 +1738,7 @@
       <c r="J4">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>43.134593799999998</v>
       </c>
     </row>
@@ -1702,7 +1773,7 @@
       <c r="J5">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>44.9234182</v>
       </c>
     </row>
@@ -1993,7 +2064,7 @@
       <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14">
         <v>71.247</v>
       </c>
       <c r="D14">
@@ -2017,7 +2088,7 @@
       <c r="J14">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="4">
         <v>66.587446200000002</v>
       </c>
     </row>
@@ -2028,7 +2099,7 @@
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15">
         <v>72.135999999999996</v>
       </c>
       <c r="D15">
@@ -2052,7 +2123,7 @@
       <c r="J15">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="4">
         <v>67.418305599999997</v>
       </c>
     </row>
@@ -2063,7 +2134,7 @@
       <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16">
         <v>73.816000000000003</v>
       </c>
       <c r="D16">
@@ -2087,7 +2158,7 @@
       <c r="J16">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="4">
         <v>68.988433600000008</v>
       </c>
     </row>
@@ -2098,7 +2169,7 @@
       <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>74.86099999999999</v>
       </c>
       <c r="D17">
@@ -2122,7 +2193,7 @@
       <c r="J17">
         <v>0.93459999999999999</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="4">
         <v>69.965090599999996</v>
       </c>
     </row>
@@ -2133,7 +2204,7 @@
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18">
         <v>75.509</v>
       </c>
       <c r="D18">
@@ -2157,7 +2228,7 @@
       <c r="J18">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="4">
         <v>70.948256400000005</v>
       </c>
     </row>
@@ -2168,7 +2239,7 @@
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19">
         <v>77.284999999999982</v>
       </c>
       <c r="D19">
@@ -2192,7 +2263,7 @@
       <c r="J19">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="4">
         <v>72.616985999999983</v>
       </c>
     </row>
@@ -2203,7 +2274,7 @@
       <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20">
         <v>81.393000000000001</v>
       </c>
       <c r="D20">
@@ -2227,7 +2298,7 @@
       <c r="J20">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="4">
         <v>76.476862800000006</v>
       </c>
     </row>
@@ -2238,7 +2309,7 @@
       <c r="B21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21">
         <v>85.838999999999999</v>
       </c>
       <c r="D21">
@@ -2262,7 +2333,7 @@
       <c r="J21">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="4">
         <v>80.654324399999993</v>
       </c>
     </row>
@@ -2273,7 +2344,7 @@
       <c r="B22" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22">
         <v>88.384000000000015</v>
       </c>
       <c r="D22">
@@ -2297,7 +2368,7 @@
       <c r="J22">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="4">
         <v>83.045606400000011</v>
       </c>
     </row>
@@ -2308,7 +2379,7 @@
       <c r="B23" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23">
         <v>92.35799999999999</v>
       </c>
       <c r="D23">
@@ -2332,7 +2403,7 @@
       <c r="J23">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="4">
         <v>86.779576799999987</v>
       </c>
     </row>
@@ -2343,7 +2414,7 @@
       <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24">
         <v>72.210000000000008</v>
       </c>
       <c r="D24">
@@ -2367,7 +2438,7 @@
       <c r="J24">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="4">
         <v>67.848516000000004</v>
       </c>
     </row>
@@ -2378,7 +2449,7 @@
       <c r="B25" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25">
         <v>72.528999999999996</v>
       </c>
       <c r="D25">
@@ -2402,7 +2473,7 @@
       <c r="J25">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="4">
         <v>68.1482484</v>
       </c>
     </row>
@@ -2413,7 +2484,7 @@
       <c r="B26" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26">
         <v>73.031999999999996</v>
       </c>
       <c r="D26">
@@ -2437,7 +2508,7 @@
       <c r="J26">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="4">
         <v>68.620867199999992</v>
       </c>
     </row>
@@ -2448,7 +2519,7 @@
       <c r="B27" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27">
         <v>74.566000000000017</v>
       </c>
       <c r="D27">
@@ -2472,7 +2543,7 @@
       <c r="J27">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="4">
         <v>70.062213600000021</v>
       </c>
     </row>
@@ -2483,7 +2554,7 @@
       <c r="B28" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28">
         <v>76.055000000000007</v>
       </c>
       <c r="D28">
@@ -2507,7 +2578,7 @@
       <c r="J28">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="4">
         <v>71.461278000000007</v>
       </c>
     </row>
@@ -2518,7 +2589,7 @@
       <c r="B29" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29">
         <v>77.760000000000005</v>
       </c>
       <c r="D29">
@@ -2542,7 +2613,7 @@
       <c r="J29">
         <v>0.93959999999999999</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="4">
         <v>73.063296000000008</v>
       </c>
     </row>
@@ -3277,7 +3348,7 @@
       <c r="J50">
         <v>1</v>
       </c>
-      <c r="K50" s="5">
+      <c r="K50" s="4">
         <v>38.161999999999999</v>
       </c>
     </row>
@@ -3312,7 +3383,7 @@
       <c r="J51">
         <v>1</v>
       </c>
-      <c r="K51" s="5">
+      <c r="K51" s="4">
         <v>42.145000000000003</v>
       </c>
     </row>
@@ -3347,7 +3418,7 @@
       <c r="J52">
         <v>1</v>
       </c>
-      <c r="K52" s="5">
+      <c r="K52" s="4">
         <v>42.889000000000003</v>
       </c>
     </row>
@@ -3382,7 +3453,7 @@
       <c r="J53">
         <v>1</v>
       </c>
-      <c r="K53" s="5">
+      <c r="K53" s="4">
         <v>42.917000000000002</v>
       </c>
     </row>
@@ -3417,7 +3488,7 @@
       <c r="J54">
         <v>1</v>
       </c>
-      <c r="K54" s="5">
+      <c r="K54" s="4">
         <v>43.091999999999999</v>
       </c>
     </row>
@@ -3452,7 +3523,7 @@
       <c r="J55">
         <v>1</v>
       </c>
-      <c r="K55" s="5">
+      <c r="K55" s="4">
         <v>43.738</v>
       </c>
     </row>
@@ -3487,7 +3558,7 @@
       <c r="J56">
         <v>1</v>
       </c>
-      <c r="K56" s="5">
+      <c r="K56" s="4">
         <v>45.027999999999999</v>
       </c>
     </row>
@@ -3522,7 +3593,7 @@
       <c r="J57">
         <v>1</v>
       </c>
-      <c r="K57" s="5">
+      <c r="K57" s="4">
         <v>45.805</v>
       </c>
     </row>
@@ -3557,7 +3628,7 @@
       <c r="J58">
         <v>1</v>
       </c>
-      <c r="K58" s="5">
+      <c r="K58" s="4">
         <v>46.59</v>
       </c>
     </row>
@@ -3592,7 +3663,7 @@
       <c r="J59">
         <v>1</v>
       </c>
-      <c r="K59" s="5">
+      <c r="K59" s="4">
         <v>48.097999999999999</v>
       </c>
     </row>
@@ -3627,7 +3698,7 @@
       <c r="J60">
         <v>1</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K60" s="4">
         <v>48.561999999999998</v>
       </c>
     </row>
@@ -3662,7 +3733,7 @@
       <c r="J61">
         <v>1</v>
       </c>
-      <c r="K61" s="5">
+      <c r="K61" s="4">
         <v>49.037999999999997</v>
       </c>
     </row>
@@ -3697,7 +3768,7 @@
       <c r="J62">
         <v>1</v>
       </c>
-      <c r="K62" s="5">
+      <c r="K62" s="4">
         <v>62.055</v>
       </c>
     </row>
@@ -3732,7 +3803,7 @@
       <c r="J63">
         <v>1</v>
       </c>
-      <c r="K63" s="5">
+      <c r="K63" s="4">
         <v>38.378</v>
       </c>
     </row>
@@ -3767,7 +3838,7 @@
       <c r="J64">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K64" s="5">
+      <c r="K64" s="4">
         <v>41.856733799999994</v>
       </c>
     </row>
@@ -3802,7 +3873,7 @@
       <c r="J65">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K65" s="5">
+      <c r="K65" s="4">
         <v>42.337436400000001</v>
       </c>
     </row>
@@ -3837,7 +3908,7 @@
       <c r="J66">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K66" s="5">
+      <c r="K66" s="4">
         <v>42.3888696</v>
       </c>
     </row>
@@ -3872,7 +3943,7 @@
       <c r="J67">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K67" s="5">
+      <c r="K67" s="4">
         <v>42.598558799999999</v>
       </c>
     </row>
@@ -4443,7 +4514,7 @@
       <c r="B84" t="s">
         <v>29</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84">
         <v>69.228999999999999</v>
       </c>
       <c r="D84">
@@ -4467,7 +4538,7 @@
       <c r="J84">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K84" s="5">
+      <c r="K84" s="4">
         <v>68.474403899999999</v>
       </c>
     </row>
@@ -4478,7 +4549,7 @@
       <c r="B85" t="s">
         <v>62</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85">
         <v>71.085000000000008</v>
       </c>
       <c r="D85">
@@ -4502,7 +4573,7 @@
       <c r="J85">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K85" s="5">
+      <c r="K85" s="4">
         <v>70.310173500000005</v>
       </c>
     </row>
@@ -4513,7 +4584,7 @@
       <c r="B86" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86">
         <v>71.521000000000001</v>
       </c>
       <c r="D86">
@@ -4537,7 +4608,7 @@
       <c r="J86">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K86" s="5">
+      <c r="K86" s="4">
         <v>70.741421099999997</v>
       </c>
     </row>
@@ -4548,7 +4619,7 @@
       <c r="B87" t="s">
         <v>35</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87">
         <v>72.444000000000003</v>
       </c>
       <c r="D87">
@@ -4572,7 +4643,7 @@
       <c r="J87">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K87" s="5">
+      <c r="K87" s="4">
         <v>71.654360400000002</v>
       </c>
     </row>
@@ -4583,7 +4654,7 @@
       <c r="B88" t="s">
         <v>29</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88">
         <v>73.335999999999999</v>
       </c>
       <c r="D88">
@@ -4607,7 +4678,7 @@
       <c r="J88">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K88" s="5">
+      <c r="K88" s="4">
         <v>72.536637599999992</v>
       </c>
     </row>
@@ -4618,7 +4689,7 @@
       <c r="B89" t="s">
         <v>31</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89">
         <v>74.376999999999995</v>
       </c>
       <c r="D89">
@@ -4642,7 +4713,7 @@
       <c r="J89">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K89" s="5">
+      <c r="K89" s="4">
         <v>73.566290699999996</v>
       </c>
     </row>
@@ -4653,7 +4724,7 @@
       <c r="B90" t="s">
         <v>21</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90">
         <v>74.407000000000011</v>
       </c>
       <c r="D90">
@@ -4677,7 +4748,7 @@
       <c r="J90">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K90" s="5">
+      <c r="K90" s="4">
         <v>73.595963700000013</v>
       </c>
     </row>
@@ -4688,7 +4759,7 @@
       <c r="B91" t="s">
         <v>32</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91">
         <v>75.204999999999998</v>
       </c>
       <c r="D91">
@@ -4712,7 +4783,7 @@
       <c r="J91">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K91" s="5">
+      <c r="K91" s="4">
         <v>74.385265500000003</v>
       </c>
     </row>
@@ -4723,7 +4794,7 @@
       <c r="B92" t="s">
         <v>54</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92">
         <v>76.42</v>
       </c>
       <c r="D92">
@@ -4747,7 +4818,7 @@
       <c r="J92">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K92" s="5">
+      <c r="K92" s="4">
         <v>75.587022000000005</v>
       </c>
     </row>
@@ -4758,7 +4829,7 @@
       <c r="B93" t="s">
         <v>57</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93">
         <v>76.629000000000005</v>
       </c>
       <c r="D93">
@@ -4782,7 +4853,7 @@
       <c r="J93">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K93" s="5">
+      <c r="K93" s="4">
         <v>75.79374390000001</v>
       </c>
     </row>
@@ -4793,7 +4864,7 @@
       <c r="B94" t="s">
         <v>21</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94">
         <v>76.689000000000007</v>
       </c>
       <c r="D94">
@@ -4817,7 +4888,7 @@
       <c r="J94">
         <v>1</v>
       </c>
-      <c r="K94" s="5">
+      <c r="K94" s="4">
         <v>76.689000000000007</v>
       </c>
     </row>
@@ -4828,7 +4899,7 @@
       <c r="B95" t="s">
         <v>23</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95">
         <v>77.05</v>
       </c>
       <c r="D95">
@@ -4852,7 +4923,7 @@
       <c r="J95">
         <v>1</v>
       </c>
-      <c r="K95" s="5">
+      <c r="K95" s="4">
         <v>77.05</v>
       </c>
     </row>
@@ -4863,7 +4934,7 @@
       <c r="B96" t="s">
         <v>43</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96">
         <v>81.008999999999986</v>
       </c>
       <c r="D96">
@@ -4887,7 +4958,7 @@
       <c r="J96">
         <v>1</v>
       </c>
-      <c r="K96" s="5">
+      <c r="K96" s="4">
         <v>81.008999999999986</v>
       </c>
     </row>
@@ -4898,7 +4969,7 @@
       <c r="B97" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97">
         <v>81.433999999999997</v>
       </c>
       <c r="D97">
@@ -4922,7 +4993,7 @@
       <c r="J97">
         <v>1</v>
       </c>
-      <c r="K97" s="5">
+      <c r="K97" s="4">
         <v>81.433999999999997</v>
       </c>
     </row>
@@ -4933,7 +5004,7 @@
       <c r="B98" t="s">
         <v>51</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98">
         <v>81.798999999999992</v>
       </c>
       <c r="D98">
@@ -4957,7 +5028,7 @@
       <c r="J98">
         <v>1</v>
       </c>
-      <c r="K98" s="5">
+      <c r="K98" s="4">
         <v>81.798999999999992</v>
       </c>
     </row>
@@ -4968,7 +5039,7 @@
       <c r="B99" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99">
         <v>86.73299999999999</v>
       </c>
       <c r="D99">
@@ -4992,7 +5063,7 @@
       <c r="J99">
         <v>1</v>
       </c>
-      <c r="K99" s="5">
+      <c r="K99" s="4">
         <v>86.73299999999999</v>
       </c>
     </row>
@@ -5003,7 +5074,7 @@
       <c r="B100" t="s">
         <v>39</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100">
         <v>86.921000000000006</v>
       </c>
       <c r="D100">
@@ -5027,7 +5098,7 @@
       <c r="J100">
         <v>1</v>
       </c>
-      <c r="K100" s="5">
+      <c r="K100" s="4">
         <v>86.921000000000006</v>
       </c>
     </row>
@@ -5038,7 +5109,7 @@
       <c r="B101" t="s">
         <v>41</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101">
         <v>87.647999999999996</v>
       </c>
       <c r="D101">
@@ -5062,7 +5133,7 @@
       <c r="J101">
         <v>1</v>
       </c>
-      <c r="K101" s="5">
+      <c r="K101" s="4">
         <v>87.647999999999996</v>
       </c>
     </row>
@@ -5073,7 +5144,7 @@
       <c r="B102" t="s">
         <v>29</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102">
         <v>69.947000000000003</v>
       </c>
       <c r="D102">
@@ -5097,7 +5168,7 @@
       <c r="J102">
         <v>1</v>
       </c>
-      <c r="K102" s="5">
+      <c r="K102" s="4">
         <v>69.947000000000003</v>
       </c>
     </row>
@@ -5108,7 +5179,7 @@
       <c r="B103" t="s">
         <v>62</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103">
         <v>70.699999999999989</v>
       </c>
       <c r="D103">
@@ -5132,7 +5203,7 @@
       <c r="J103">
         <v>1</v>
       </c>
-      <c r="K103" s="5">
+      <c r="K103" s="4">
         <v>70.699999999999989</v>
       </c>
     </row>
@@ -5143,7 +5214,7 @@
       <c r="B104" t="s">
         <v>32</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104">
         <v>71.445000000000007</v>
       </c>
       <c r="D104">
@@ -5167,7 +5238,7 @@
       <c r="J104">
         <v>1</v>
       </c>
-      <c r="K104" s="5">
+      <c r="K104" s="4">
         <v>71.445000000000007</v>
       </c>
     </row>
@@ -5178,7 +5249,7 @@
       <c r="B105" t="s">
         <v>35</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105">
         <v>71.918000000000006</v>
       </c>
       <c r="D105">
@@ -5202,7 +5273,7 @@
       <c r="J105">
         <v>1</v>
       </c>
-      <c r="K105" s="5">
+      <c r="K105" s="4">
         <v>71.918000000000006</v>
       </c>
     </row>
@@ -5213,7 +5284,7 @@
       <c r="B106" t="s">
         <v>29</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106">
         <v>73.785000000000011</v>
       </c>
       <c r="D106">
@@ -5237,7 +5308,7 @@
       <c r="J106">
         <v>1</v>
       </c>
-      <c r="K106" s="5">
+      <c r="K106" s="4">
         <v>73.785000000000011</v>
       </c>
     </row>
@@ -5248,7 +5319,7 @@
       <c r="B107" t="s">
         <v>31</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107">
         <v>75.076000000000008</v>
       </c>
       <c r="D107">
@@ -5272,7 +5343,7 @@
       <c r="J107">
         <v>1</v>
       </c>
-      <c r="K107" s="5">
+      <c r="K107" s="4">
         <v>75.076000000000008</v>
       </c>
     </row>
@@ -6952,7 +7023,7 @@
       <c r="J155">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K155" s="5">
+      <c r="K155" s="4">
         <v>38.7568944</v>
       </c>
     </row>
@@ -6987,7 +7058,7 @@
       <c r="J156">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K156" s="5">
+      <c r="K156" s="4">
         <v>39.649062600000001</v>
       </c>
     </row>
@@ -7022,7 +7093,7 @@
       <c r="J157">
         <v>0.98909999999999987</v>
       </c>
-      <c r="K157" s="5">
+      <c r="K157" s="4">
         <v>40.952696400000001</v>
       </c>
     </row>
@@ -7057,7 +7128,7 @@
       <c r="J158">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K158" s="5">
+      <c r="K158" s="4">
         <v>41.892341399999999</v>
       </c>
     </row>
@@ -7092,7 +7163,7 @@
       <c r="J159">
         <v>0.98909999999999998</v>
       </c>
-      <c r="K159" s="5">
+      <c r="K159" s="4">
         <v>49.137498900000004</v>
       </c>
     </row>
@@ -7558,7 +7629,7 @@
       <c r="B173" t="s">
         <v>21</v>
       </c>
-      <c r="C173" s="4">
+      <c r="C173">
         <v>66.015000000000001</v>
       </c>
       <c r="D173">
@@ -7582,7 +7653,7 @@
       <c r="J173">
         <v>1</v>
       </c>
-      <c r="K173" s="5">
+      <c r="K173" s="4">
         <v>66.015000000000001</v>
       </c>
     </row>
@@ -7593,7 +7664,7 @@
       <c r="B174" t="s">
         <v>81</v>
       </c>
-      <c r="C174" s="4">
+      <c r="C174">
         <v>66.668999999999997</v>
       </c>
       <c r="D174">
@@ -7617,7 +7688,7 @@
       <c r="J174">
         <v>1</v>
       </c>
-      <c r="K174" s="5">
+      <c r="K174" s="4">
         <v>66.668999999999997</v>
       </c>
     </row>
@@ -7628,7 +7699,7 @@
       <c r="B175" t="s">
         <v>21</v>
       </c>
-      <c r="C175" s="4">
+      <c r="C175">
         <v>66.817999999999998</v>
       </c>
       <c r="D175">
@@ -7652,7 +7723,7 @@
       <c r="J175">
         <v>1</v>
       </c>
-      <c r="K175" s="5">
+      <c r="K175" s="4">
         <v>66.817999999999998</v>
       </c>
     </row>
@@ -7663,7 +7734,7 @@
       <c r="B176" t="s">
         <v>28</v>
       </c>
-      <c r="C176" s="4">
+      <c r="C176">
         <v>68.926000000000002</v>
       </c>
       <c r="D176">
@@ -7687,7 +7758,7 @@
       <c r="J176">
         <v>1</v>
       </c>
-      <c r="K176" s="5">
+      <c r="K176" s="4">
         <v>68.926000000000002</v>
       </c>
     </row>
@@ -7698,7 +7769,7 @@
       <c r="B177" t="s">
         <v>14</v>
       </c>
-      <c r="C177" s="4">
+      <c r="C177">
         <v>69.573000000000008</v>
       </c>
       <c r="D177">
@@ -7722,7 +7793,7 @@
       <c r="J177">
         <v>1</v>
       </c>
-      <c r="K177" s="5">
+      <c r="K177" s="4">
         <v>69.573000000000008</v>
       </c>
     </row>
@@ -7733,7 +7804,7 @@
       <c r="B178" t="s">
         <v>32</v>
       </c>
-      <c r="C178" s="4">
+      <c r="C178">
         <v>70.394999999999996</v>
       </c>
       <c r="D178">
@@ -7757,7 +7828,7 @@
       <c r="J178">
         <v>1</v>
       </c>
-      <c r="K178" s="5">
+      <c r="K178" s="4">
         <v>70.394999999999996</v>
       </c>
     </row>
@@ -7768,7 +7839,7 @@
       <c r="B179" t="s">
         <v>76</v>
       </c>
-      <c r="C179" s="4">
+      <c r="C179">
         <v>70.480000000000018</v>
       </c>
       <c r="D179">
@@ -7792,7 +7863,7 @@
       <c r="J179">
         <v>1</v>
       </c>
-      <c r="K179" s="5">
+      <c r="K179" s="4">
         <v>70.480000000000018</v>
       </c>
     </row>
@@ -7803,7 +7874,7 @@
       <c r="B180" t="s">
         <v>57</v>
       </c>
-      <c r="C180" s="4">
+      <c r="C180">
         <v>72.302999999999997</v>
       </c>
       <c r="D180">
@@ -7827,7 +7898,7 @@
       <c r="J180">
         <v>1</v>
       </c>
-      <c r="K180" s="5">
+      <c r="K180" s="4">
         <v>72.302999999999997</v>
       </c>
     </row>
@@ -7838,7 +7909,7 @@
       <c r="B181" t="s">
         <v>21</v>
       </c>
-      <c r="C181" s="4">
+      <c r="C181">
         <v>73.170999999999992</v>
       </c>
       <c r="D181">
@@ -7862,7 +7933,7 @@
       <c r="J181">
         <v>1</v>
       </c>
-      <c r="K181" s="5">
+      <c r="K181" s="4">
         <v>73.170999999999992</v>
       </c>
     </row>
@@ -7873,7 +7944,7 @@
       <c r="B182" t="s">
         <v>29</v>
       </c>
-      <c r="C182" s="4">
+      <c r="C182">
         <v>73.338000000000008</v>
       </c>
       <c r="D182">
@@ -7897,7 +7968,7 @@
       <c r="J182">
         <v>1</v>
       </c>
-      <c r="K182" s="5">
+      <c r="K182" s="4">
         <v>73.338000000000008</v>
       </c>
     </row>
@@ -7908,7 +7979,7 @@
       <c r="B183" t="s">
         <v>18</v>
       </c>
-      <c r="C183" s="4">
+      <c r="C183">
         <v>74.001000000000005</v>
       </c>
       <c r="D183">
@@ -7932,7 +8003,7 @@
       <c r="J183">
         <v>1</v>
       </c>
-      <c r="K183" s="5">
+      <c r="K183" s="4">
         <v>74.001000000000005</v>
       </c>
     </row>
@@ -7943,7 +8014,7 @@
       <c r="B184" t="s">
         <v>21</v>
       </c>
-      <c r="C184" s="4">
+      <c r="C184">
         <v>74.214999999999989</v>
       </c>
       <c r="D184">
@@ -7967,7 +8038,7 @@
       <c r="J184">
         <v>1</v>
       </c>
-      <c r="K184" s="5">
+      <c r="K184" s="4">
         <v>74.214999999999989</v>
       </c>
     </row>
@@ -7978,7 +8049,7 @@
       <c r="B185" t="s">
         <v>31</v>
       </c>
-      <c r="C185" s="4">
+      <c r="C185">
         <v>76.278000000000006</v>
       </c>
       <c r="D185">
@@ -8002,7 +8073,7 @@
       <c r="J185">
         <v>1</v>
       </c>
-      <c r="K185" s="5">
+      <c r="K185" s="4">
         <v>76.278000000000006</v>
       </c>
     </row>
@@ -8013,7 +8084,7 @@
       <c r="B186" t="s">
         <v>8</v>
       </c>
-      <c r="C186" s="4">
+      <c r="C186">
         <v>81.154000000000011</v>
       </c>
       <c r="D186">
@@ -8037,7 +8108,7 @@
       <c r="J186">
         <v>1</v>
       </c>
-      <c r="K186" s="5">
+      <c r="K186" s="4">
         <v>81.154000000000011</v>
       </c>
     </row>
@@ -8048,7 +8119,7 @@
       <c r="B187" t="s">
         <v>67</v>
       </c>
-      <c r="C187" s="4">
+      <c r="C187">
         <v>81.426000000000002</v>
       </c>
       <c r="D187">
@@ -8072,7 +8143,7 @@
       <c r="J187">
         <v>1</v>
       </c>
-      <c r="K187" s="5">
+      <c r="K187" s="4">
         <v>81.426000000000002</v>
       </c>
     </row>
@@ -8083,7 +8154,7 @@
       <c r="B188" t="s">
         <v>6</v>
       </c>
-      <c r="C188" s="4">
+      <c r="C188">
         <v>93.355000000000004</v>
       </c>
       <c r="D188">
@@ -8107,7 +8178,7 @@
       <c r="J188">
         <v>1</v>
       </c>
-      <c r="K188" s="5">
+      <c r="K188" s="4">
         <v>93.355000000000004</v>
       </c>
     </row>
@@ -8118,7 +8189,7 @@
       <c r="B189" t="s">
         <v>21</v>
       </c>
-      <c r="C189" s="4">
+      <c r="C189">
         <v>66.186999999999998</v>
       </c>
       <c r="D189">
@@ -8142,7 +8213,7 @@
       <c r="J189">
         <v>1</v>
       </c>
-      <c r="K189" s="5">
+      <c r="K189" s="4">
         <v>66.186999999999998</v>
       </c>
     </row>
@@ -8153,7 +8224,7 @@
       <c r="B190" t="s">
         <v>21</v>
       </c>
-      <c r="C190" s="4">
+      <c r="C190">
         <v>66.45</v>
       </c>
       <c r="D190">
@@ -8177,7 +8248,7 @@
       <c r="J190">
         <v>1</v>
       </c>
-      <c r="K190" s="5">
+      <c r="K190" s="4">
         <v>66.45</v>
       </c>
     </row>
@@ -8188,7 +8259,7 @@
       <c r="B191" t="s">
         <v>81</v>
       </c>
-      <c r="C191" s="4">
+      <c r="C191">
         <v>66.830999999999989</v>
       </c>
       <c r="D191">
@@ -8212,7 +8283,7 @@
       <c r="J191">
         <v>1</v>
       </c>
-      <c r="K191" s="5">
+      <c r="K191" s="4">
         <v>66.830999999999989</v>
       </c>
     </row>
@@ -8223,7 +8294,7 @@
       <c r="B192" t="s">
         <v>28</v>
       </c>
-      <c r="C192" s="4">
+      <c r="C192">
         <v>69.037000000000006</v>
       </c>
       <c r="D192">
@@ -8247,7 +8318,7 @@
       <c r="J192">
         <v>1</v>
       </c>
-      <c r="K192" s="5">
+      <c r="K192" s="4">
         <v>69.037000000000006</v>
       </c>
     </row>
@@ -8258,7 +8329,7 @@
       <c r="B193" t="s">
         <v>32</v>
       </c>
-      <c r="C193" s="4">
+      <c r="C193">
         <v>69.819000000000003</v>
       </c>
       <c r="D193">
@@ -8282,7 +8353,7 @@
       <c r="J193">
         <v>1</v>
       </c>
-      <c r="K193" s="5">
+      <c r="K193" s="4">
         <v>69.819000000000003</v>
       </c>
     </row>
@@ -8293,7 +8364,7 @@
       <c r="B194" t="s">
         <v>14</v>
       </c>
-      <c r="C194" s="4">
+      <c r="C194">
         <v>70.423000000000002</v>
       </c>
       <c r="D194">
@@ -8317,7 +8388,7 @@
       <c r="J194">
         <v>1</v>
       </c>
-      <c r="K194" s="5">
+      <c r="K194" s="4">
         <v>70.423000000000002</v>
       </c>
     </row>
@@ -9682,7 +9753,7 @@
       <c r="J233">
         <v>1</v>
       </c>
-      <c r="K233" s="5">
+      <c r="K233" s="4">
         <v>35.756999999999998</v>
       </c>
     </row>
@@ -9717,7 +9788,7 @@
       <c r="J234">
         <v>1</v>
       </c>
-      <c r="K234" s="5">
+      <c r="K234" s="4">
         <v>37.811999999999998</v>
       </c>
     </row>
@@ -9752,7 +9823,7 @@
       <c r="J235">
         <v>1</v>
       </c>
-      <c r="K235" s="5">
+      <c r="K235" s="4">
         <v>37.860999999999997</v>
       </c>
     </row>
@@ -9787,7 +9858,7 @@
       <c r="J236">
         <v>1</v>
       </c>
-      <c r="K236" s="5">
+      <c r="K236" s="4">
         <v>38.847999999999999</v>
       </c>
     </row>
@@ -9822,7 +9893,7 @@
       <c r="J237">
         <v>1</v>
       </c>
-      <c r="K237" s="5">
+      <c r="K237" s="4">
         <v>38.848999999999997</v>
       </c>
     </row>
@@ -9857,7 +9928,7 @@
       <c r="J238">
         <v>1</v>
       </c>
-      <c r="K238" s="5">
+      <c r="K238" s="4">
         <v>39.898000000000003</v>
       </c>
     </row>
@@ -9892,7 +9963,7 @@
       <c r="J239">
         <v>1</v>
       </c>
-      <c r="K239" s="5">
+      <c r="K239" s="4">
         <v>40.369</v>
       </c>
     </row>
@@ -9927,7 +9998,7 @@
       <c r="J240">
         <v>1</v>
       </c>
-      <c r="K240" s="5">
+      <c r="K240" s="4">
         <v>41.42</v>
       </c>
     </row>
@@ -9962,7 +10033,7 @@
       <c r="J241">
         <v>1</v>
       </c>
-      <c r="K241" s="5">
+      <c r="K241" s="4">
         <v>41.832000000000001</v>
       </c>
     </row>
@@ -9997,7 +10068,7 @@
       <c r="J242">
         <v>1</v>
       </c>
-      <c r="K242" s="5">
+      <c r="K242" s="4">
         <v>42.633000000000003</v>
       </c>
     </row>
@@ -10032,7 +10103,7 @@
       <c r="J243">
         <v>1</v>
       </c>
-      <c r="K243" s="5">
+      <c r="K243" s="4">
         <v>44.247999999999998</v>
       </c>
     </row>
@@ -10067,7 +10138,7 @@
       <c r="J244">
         <v>1</v>
       </c>
-      <c r="K244" s="5">
+      <c r="K244" s="4">
         <v>44.308999999999997</v>
       </c>
     </row>
@@ -10102,7 +10173,7 @@
       <c r="J245">
         <v>1</v>
       </c>
-      <c r="K245" s="5">
+      <c r="K245" s="4">
         <v>44.319000000000003</v>
       </c>
     </row>
@@ -10137,7 +10208,7 @@
       <c r="J246">
         <v>1</v>
       </c>
-      <c r="K246" s="5">
+      <c r="K246" s="4">
         <v>45.988999999999997</v>
       </c>
     </row>
@@ -10172,7 +10243,7 @@
       <c r="J247">
         <v>1</v>
       </c>
-      <c r="K247" s="5">
+      <c r="K247" s="4">
         <v>35.960999999999999</v>
       </c>
     </row>
@@ -10207,7 +10278,7 @@
       <c r="J248">
         <v>1</v>
       </c>
-      <c r="K248" s="5">
+      <c r="K248" s="4">
         <v>38.136000000000003</v>
       </c>
     </row>
@@ -10242,7 +10313,7 @@
       <c r="J249">
         <v>1</v>
       </c>
-      <c r="K249" s="5">
+      <c r="K249" s="4">
         <v>38.296999999999997</v>
       </c>
     </row>
@@ -10277,7 +10348,7 @@
       <c r="J250">
         <v>1</v>
       </c>
-      <c r="K250" s="5">
+      <c r="K250" s="4">
         <v>38.564999999999998</v>
       </c>
     </row>
@@ -10312,7 +10383,7 @@
       <c r="J251">
         <v>1</v>
       </c>
-      <c r="K251" s="5">
+      <c r="K251" s="4">
         <v>39.241999999999997</v>
       </c>
     </row>
@@ -10347,7 +10418,7 @@
       <c r="J252">
         <v>1</v>
       </c>
-      <c r="K252" s="5">
+      <c r="K252" s="4">
         <v>39.854999999999997</v>
       </c>
     </row>
@@ -10358,7 +10429,7 @@
       <c r="B253" t="s">
         <v>21</v>
       </c>
-      <c r="C253" s="4">
+      <c r="C253">
         <v>63.614000000000004</v>
       </c>
       <c r="D253">
@@ -10382,7 +10453,7 @@
       <c r="J253">
         <v>1</v>
       </c>
-      <c r="K253" s="5">
+      <c r="K253" s="4">
         <v>63.614000000000004</v>
       </c>
     </row>
@@ -10393,7 +10464,7 @@
       <c r="B254" t="s">
         <v>32</v>
       </c>
-      <c r="C254" s="4">
+      <c r="C254">
         <v>64.85199999999999</v>
       </c>
       <c r="D254">
@@ -10417,7 +10488,7 @@
       <c r="J254">
         <v>1</v>
       </c>
-      <c r="K254" s="5">
+      <c r="K254" s="4">
         <v>64.85199999999999</v>
       </c>
     </row>
@@ -10428,7 +10499,7 @@
       <c r="B255" t="s">
         <v>16</v>
       </c>
-      <c r="C255" s="4">
+      <c r="C255">
         <v>65.47</v>
       </c>
       <c r="D255">
@@ -10452,7 +10523,7 @@
       <c r="J255">
         <v>1</v>
       </c>
-      <c r="K255" s="5">
+      <c r="K255" s="4">
         <v>65.47</v>
       </c>
     </row>
@@ -10463,7 +10534,7 @@
       <c r="B256" t="s">
         <v>57</v>
       </c>
-      <c r="C256" s="4">
+      <c r="C256">
         <v>66.475000000000009</v>
       </c>
       <c r="D256">
@@ -10487,7 +10558,7 @@
       <c r="J256">
         <v>1</v>
       </c>
-      <c r="K256" s="5">
+      <c r="K256" s="4">
         <v>66.475000000000009</v>
       </c>
     </row>
@@ -10498,7 +10569,7 @@
       <c r="B257" t="s">
         <v>110</v>
       </c>
-      <c r="C257" s="4">
+      <c r="C257">
         <v>66.89800000000001</v>
       </c>
       <c r="D257">
@@ -10522,7 +10593,7 @@
       <c r="J257">
         <v>1</v>
       </c>
-      <c r="K257" s="5">
+      <c r="K257" s="4">
         <v>66.89800000000001</v>
       </c>
     </row>
@@ -10533,7 +10604,7 @@
       <c r="B258" t="s">
         <v>21</v>
       </c>
-      <c r="C258" s="4">
+      <c r="C258">
         <v>67.228999999999999</v>
       </c>
       <c r="D258">
@@ -10557,7 +10628,7 @@
       <c r="J258">
         <v>1</v>
       </c>
-      <c r="K258" s="5">
+      <c r="K258" s="4">
         <v>67.228999999999999</v>
       </c>
     </row>
@@ -10568,7 +10639,7 @@
       <c r="B259" t="s">
         <v>29</v>
       </c>
-      <c r="C259" s="4">
+      <c r="C259">
         <v>67.457000000000008</v>
       </c>
       <c r="D259">
@@ -10592,7 +10663,7 @@
       <c r="J259">
         <v>1</v>
       </c>
-      <c r="K259" s="5">
+      <c r="K259" s="4">
         <v>67.457000000000008</v>
       </c>
     </row>
@@ -10603,7 +10674,7 @@
       <c r="B260" t="s">
         <v>31</v>
       </c>
-      <c r="C260" s="4">
+      <c r="C260">
         <v>68.153999999999996</v>
       </c>
       <c r="D260">
@@ -10627,7 +10698,7 @@
       <c r="J260">
         <v>1</v>
       </c>
-      <c r="K260" s="5">
+      <c r="K260" s="4">
         <v>68.153999999999996</v>
       </c>
     </row>
@@ -10638,7 +10709,7 @@
       <c r="B261" t="s">
         <v>81</v>
       </c>
-      <c r="C261" s="4">
+      <c r="C261">
         <v>68.447000000000003</v>
       </c>
       <c r="D261">
@@ -10662,7 +10733,7 @@
       <c r="J261">
         <v>1</v>
       </c>
-      <c r="K261" s="5">
+      <c r="K261" s="4">
         <v>68.447000000000003</v>
       </c>
     </row>
@@ -10673,7 +10744,7 @@
       <c r="B262" t="s">
         <v>29</v>
       </c>
-      <c r="C262" s="4">
+      <c r="C262">
         <v>69.265000000000001</v>
       </c>
       <c r="D262">
@@ -10697,7 +10768,7 @@
       <c r="J262">
         <v>1</v>
       </c>
-      <c r="K262" s="5">
+      <c r="K262" s="4">
         <v>69.265000000000001</v>
       </c>
     </row>
@@ -10708,7 +10779,7 @@
       <c r="B263" t="s">
         <v>43</v>
       </c>
-      <c r="C263" s="4">
+      <c r="C263">
         <v>69.540999999999983</v>
       </c>
       <c r="D263">
@@ -10732,7 +10803,7 @@
       <c r="J263">
         <v>1</v>
       </c>
-      <c r="K263" s="5">
+      <c r="K263" s="4">
         <v>69.540999999999983</v>
       </c>
     </row>
@@ -10743,7 +10814,7 @@
       <c r="B264" t="s">
         <v>92</v>
       </c>
-      <c r="C264" s="4">
+      <c r="C264">
         <v>69.978999999999999</v>
       </c>
       <c r="D264">
@@ -10767,7 +10838,7 @@
       <c r="J264">
         <v>1</v>
       </c>
-      <c r="K264" s="5">
+      <c r="K264" s="4">
         <v>69.978999999999999</v>
       </c>
     </row>
@@ -10778,7 +10849,7 @@
       <c r="B265" t="s">
         <v>57</v>
       </c>
-      <c r="C265" s="4">
+      <c r="C265">
         <v>70.297000000000011</v>
       </c>
       <c r="D265">
@@ -10802,7 +10873,7 @@
       <c r="J265">
         <v>1</v>
       </c>
-      <c r="K265" s="5">
+      <c r="K265" s="4">
         <v>70.297000000000011</v>
       </c>
     </row>
@@ -10813,7 +10884,7 @@
       <c r="B266" t="s">
         <v>34</v>
       </c>
-      <c r="C266" s="4">
+      <c r="C266">
         <v>70.311999999999998</v>
       </c>
       <c r="D266">
@@ -10837,7 +10908,7 @@
       <c r="J266">
         <v>1</v>
       </c>
-      <c r="K266" s="5">
+      <c r="K266" s="4">
         <v>70.311999999999998</v>
       </c>
     </row>
@@ -10848,7 +10919,7 @@
       <c r="B267" t="s">
         <v>81</v>
       </c>
-      <c r="C267" s="4">
+      <c r="C267">
         <v>70.515000000000001</v>
       </c>
       <c r="D267">
@@ -10872,7 +10943,7 @@
       <c r="J267">
         <v>1</v>
       </c>
-      <c r="K267" s="5">
+      <c r="K267" s="4">
         <v>70.515000000000001</v>
       </c>
     </row>
@@ -10883,7 +10954,7 @@
       <c r="B268" t="s">
         <v>14</v>
       </c>
-      <c r="C268" s="4">
+      <c r="C268">
         <v>71.25</v>
       </c>
       <c r="D268">
@@ -10907,7 +10978,7 @@
       <c r="J268">
         <v>1</v>
       </c>
-      <c r="K268" s="5">
+      <c r="K268" s="4">
         <v>71.25</v>
       </c>
     </row>
@@ -10918,7 +10989,7 @@
       <c r="B269" t="s">
         <v>67</v>
       </c>
-      <c r="C269" s="4">
+      <c r="C269">
         <v>71.405000000000001</v>
       </c>
       <c r="D269">
@@ -10942,7 +11013,7 @@
       <c r="J269">
         <v>1</v>
       </c>
-      <c r="K269" s="5">
+      <c r="K269" s="4">
         <v>71.405000000000001</v>
       </c>
     </row>
@@ -10953,7 +11024,7 @@
       <c r="B270" t="s">
         <v>76</v>
       </c>
-      <c r="C270" s="4">
+      <c r="C270">
         <v>71.685000000000002</v>
       </c>
       <c r="D270">
@@ -10977,7 +11048,7 @@
       <c r="J270">
         <v>1</v>
       </c>
-      <c r="K270" s="5">
+      <c r="K270" s="4">
         <v>71.685000000000002</v>
       </c>
     </row>
@@ -10988,7 +11059,7 @@
       <c r="B271" t="s">
         <v>23</v>
       </c>
-      <c r="C271" s="4">
+      <c r="C271">
         <v>72.650999999999996</v>
       </c>
       <c r="D271">
@@ -11012,7 +11083,7 @@
       <c r="J271">
         <v>1</v>
       </c>
-      <c r="K271" s="5">
+      <c r="K271" s="4">
         <v>72.650999999999996</v>
       </c>
     </row>
@@ -11023,7 +11094,7 @@
       <c r="B272" t="s">
         <v>76</v>
       </c>
-      <c r="C272" s="4">
+      <c r="C272">
         <v>72.887000000000015</v>
       </c>
       <c r="D272">
@@ -11047,7 +11118,7 @@
       <c r="J272">
         <v>1</v>
       </c>
-      <c r="K272" s="5">
+      <c r="K272" s="4">
         <v>72.887000000000015</v>
       </c>
     </row>
@@ -11058,7 +11129,7 @@
       <c r="B273" t="s">
         <v>43</v>
       </c>
-      <c r="C273" s="4">
+      <c r="C273">
         <v>73.710000000000008</v>
       </c>
       <c r="D273">
@@ -11082,7 +11153,7 @@
       <c r="J273">
         <v>1</v>
       </c>
-      <c r="K273" s="5">
+      <c r="K273" s="4">
         <v>73.710000000000008</v>
       </c>
     </row>
@@ -11093,7 +11164,7 @@
       <c r="B274" t="s">
         <v>99</v>
       </c>
-      <c r="C274" s="4">
+      <c r="C274">
         <v>75.132999999999996</v>
       </c>
       <c r="D274">
@@ -11117,7 +11188,7 @@
       <c r="J274">
         <v>1</v>
       </c>
-      <c r="K274" s="5">
+      <c r="K274" s="4">
         <v>75.132999999999996</v>
       </c>
     </row>
@@ -11128,7 +11199,7 @@
       <c r="B275" t="s">
         <v>43</v>
       </c>
-      <c r="C275" s="4">
+      <c r="C275">
         <v>76.853000000000009</v>
       </c>
       <c r="D275">
@@ -11152,7 +11223,7 @@
       <c r="J275">
         <v>1</v>
       </c>
-      <c r="K275" s="5">
+      <c r="K275" s="4">
         <v>76.853000000000009</v>
       </c>
     </row>
@@ -11163,7 +11234,7 @@
       <c r="B276" t="s">
         <v>6</v>
       </c>
-      <c r="C276" s="4">
+      <c r="C276">
         <v>78.911000000000001</v>
       </c>
       <c r="D276">
@@ -11187,7 +11258,7 @@
       <c r="J276">
         <v>1</v>
       </c>
-      <c r="K276" s="5">
+      <c r="K276" s="4">
         <v>78.911000000000001</v>
       </c>
     </row>
@@ -11198,7 +11269,7 @@
       <c r="B277" t="s">
         <v>21</v>
       </c>
-      <c r="C277" s="4">
+      <c r="C277">
         <v>63.467999999999996</v>
       </c>
       <c r="D277">
@@ -11222,7 +11293,7 @@
       <c r="J277">
         <v>1</v>
       </c>
-      <c r="K277" s="5">
+      <c r="K277" s="4">
         <v>63.467999999999996</v>
       </c>
     </row>
@@ -11233,7 +11304,7 @@
       <c r="B278" t="s">
         <v>32</v>
       </c>
-      <c r="C278" s="4">
+      <c r="C278">
         <v>64.812999999999988</v>
       </c>
       <c r="D278">
@@ -11257,7 +11328,7 @@
       <c r="J278">
         <v>1</v>
       </c>
-      <c r="K278" s="5">
+      <c r="K278" s="4">
         <v>64.812999999999988</v>
       </c>
     </row>
@@ -11268,7 +11339,7 @@
       <c r="B279" t="s">
         <v>16</v>
       </c>
-      <c r="C279" s="4">
+      <c r="C279">
         <v>65.808000000000007</v>
       </c>
       <c r="D279">
@@ -11292,7 +11363,7 @@
       <c r="J279">
         <v>1</v>
       </c>
-      <c r="K279" s="5">
+      <c r="K279" s="4">
         <v>65.808000000000007</v>
       </c>
     </row>
@@ -11303,7 +11374,7 @@
       <c r="B280" t="s">
         <v>110</v>
       </c>
-      <c r="C280" s="4">
+      <c r="C280">
         <v>67.039000000000001</v>
       </c>
       <c r="D280">
@@ -11327,7 +11398,7 @@
       <c r="J280">
         <v>1</v>
       </c>
-      <c r="K280" s="5">
+      <c r="K280" s="4">
         <v>67.039000000000001</v>
       </c>
     </row>
@@ -11338,7 +11409,7 @@
       <c r="B281" t="s">
         <v>57</v>
       </c>
-      <c r="C281" s="4">
+      <c r="C281">
         <v>67.334999999999994</v>
       </c>
       <c r="D281">
@@ -11362,7 +11433,7 @@
       <c r="J281">
         <v>1</v>
       </c>
-      <c r="K281" s="5">
+      <c r="K281" s="4">
         <v>67.334999999999994</v>
       </c>
     </row>
@@ -11373,7 +11444,7 @@
       <c r="B282" t="s">
         <v>21</v>
       </c>
-      <c r="C282" s="4">
+      <c r="C282">
         <v>67.745000000000005</v>
       </c>
       <c r="D282">
@@ -11397,7 +11468,7 @@
       <c r="J282">
         <v>1</v>
       </c>
-      <c r="K282" s="5">
+      <c r="K282" s="4">
         <v>67.745000000000005</v>
       </c>
     </row>
@@ -12587,7 +12658,7 @@
       <c r="J316">
         <v>1</v>
       </c>
-      <c r="K316" s="5">
+      <c r="K316" s="4">
         <v>37.091000000000001</v>
       </c>
     </row>
@@ -12622,7 +12693,7 @@
       <c r="J317">
         <v>1</v>
       </c>
-      <c r="K317" s="5">
+      <c r="K317" s="4">
         <v>37.372</v>
       </c>
     </row>
@@ -12657,7 +12728,7 @@
       <c r="J318">
         <v>1</v>
       </c>
-      <c r="K318" s="5">
+      <c r="K318" s="4">
         <v>38.088999999999999</v>
       </c>
     </row>
@@ -12692,7 +12763,7 @@
       <c r="J319">
         <v>1</v>
       </c>
-      <c r="K319" s="5">
+      <c r="K319" s="4">
         <v>38.619</v>
       </c>
     </row>
@@ -12727,7 +12798,7 @@
       <c r="J320">
         <v>1</v>
       </c>
-      <c r="K320" s="5">
+      <c r="K320" s="4">
         <v>38.841000000000001</v>
       </c>
     </row>
@@ -12762,7 +12833,7 @@
       <c r="J321">
         <v>1</v>
       </c>
-      <c r="K321" s="5">
+      <c r="K321" s="4">
         <v>39.112000000000002</v>
       </c>
     </row>
@@ -12797,7 +12868,7 @@
       <c r="J322">
         <v>1</v>
       </c>
-      <c r="K322" s="5">
+      <c r="K322" s="4">
         <v>39.793999999999997</v>
       </c>
     </row>
@@ -12832,7 +12903,7 @@
       <c r="J323">
         <v>1</v>
       </c>
-      <c r="K323" s="5">
+      <c r="K323" s="4">
         <v>42.497</v>
       </c>
     </row>
@@ -12867,7 +12938,7 @@
       <c r="J324">
         <v>1</v>
       </c>
-      <c r="K324" s="5">
+      <c r="K324" s="4">
         <v>43.281999999999996</v>
       </c>
     </row>
@@ -12902,7 +12973,7 @@
       <c r="J325">
         <v>1</v>
       </c>
-      <c r="K325" s="5">
+      <c r="K325" s="4">
         <v>43.426000000000002</v>
       </c>
     </row>
@@ -12937,7 +13008,7 @@
       <c r="J326">
         <v>1</v>
       </c>
-      <c r="K326" s="5">
+      <c r="K326" s="4">
         <v>49.094000000000001</v>
       </c>
     </row>
@@ -12972,7 +13043,7 @@
       <c r="J327">
         <v>1</v>
       </c>
-      <c r="K327" s="5">
+      <c r="K327" s="4">
         <v>37.252000000000002</v>
       </c>
     </row>
@@ -13007,7 +13078,7 @@
       <c r="J328">
         <v>1</v>
       </c>
-      <c r="K328" s="5">
+      <c r="K328" s="4">
         <v>37.366999999999997</v>
       </c>
     </row>
@@ -13042,7 +13113,7 @@
       <c r="J329">
         <v>1</v>
       </c>
-      <c r="K329" s="5">
+      <c r="K329" s="4">
         <v>37.890999999999998</v>
       </c>
     </row>
@@ -13077,7 +13148,7 @@
       <c r="J330">
         <v>1</v>
       </c>
-      <c r="K330" s="5">
+      <c r="K330" s="4">
         <v>38.292999999999999</v>
       </c>
     </row>
@@ -13112,7 +13183,7 @@
       <c r="J331">
         <v>1</v>
       </c>
-      <c r="K331" s="5">
+      <c r="K331" s="4">
         <v>38.920999999999999</v>
       </c>
     </row>
@@ -13147,7 +13218,7 @@
       <c r="J332">
         <v>1</v>
       </c>
-      <c r="K332" s="5">
+      <c r="K332" s="4">
         <v>39.24</v>
       </c>
     </row>
@@ -13158,7 +13229,7 @@
       <c r="B333" t="s">
         <v>21</v>
       </c>
-      <c r="C333" s="4">
+      <c r="C333">
         <v>63.845999999999997</v>
       </c>
       <c r="D333">
@@ -13182,7 +13253,7 @@
       <c r="J333">
         <v>1</v>
       </c>
-      <c r="K333" s="5">
+      <c r="K333" s="4">
         <v>63.845999999999997</v>
       </c>
     </row>
@@ -13193,7 +13264,7 @@
       <c r="B334" t="s">
         <v>14</v>
       </c>
-      <c r="C334" s="4">
+      <c r="C334">
         <v>64.623999999999995</v>
       </c>
       <c r="D334">
@@ -13217,7 +13288,7 @@
       <c r="J334">
         <v>1</v>
       </c>
-      <c r="K334" s="5">
+      <c r="K334" s="4">
         <v>64.623999999999995</v>
       </c>
     </row>
@@ -13228,7 +13299,7 @@
       <c r="B335" t="s">
         <v>57</v>
       </c>
-      <c r="C335" s="4">
+      <c r="C335">
         <v>64.887999999999991</v>
       </c>
       <c r="D335">
@@ -13252,7 +13323,7 @@
       <c r="J335">
         <v>1</v>
       </c>
-      <c r="K335" s="5">
+      <c r="K335" s="4">
         <v>64.887999999999991</v>
       </c>
     </row>
@@ -13263,7 +13334,7 @@
       <c r="B336" t="s">
         <v>23</v>
       </c>
-      <c r="C336" s="4">
+      <c r="C336">
         <v>65.23399999999998</v>
       </c>
       <c r="D336">
@@ -13287,7 +13358,7 @@
       <c r="J336">
         <v>1</v>
       </c>
-      <c r="K336" s="5">
+      <c r="K336" s="4">
         <v>65.23399999999998</v>
       </c>
     </row>
@@ -13298,7 +13369,7 @@
       <c r="B337" t="s">
         <v>16</v>
       </c>
-      <c r="C337" s="4">
+      <c r="C337">
         <v>66.284999999999997</v>
       </c>
       <c r="D337">
@@ -13322,7 +13393,7 @@
       <c r="J337">
         <v>1</v>
       </c>
-      <c r="K337" s="5">
+      <c r="K337" s="4">
         <v>66.284999999999997</v>
       </c>
     </row>
@@ -13333,7 +13404,7 @@
       <c r="B338" t="s">
         <v>8</v>
       </c>
-      <c r="C338" s="4">
+      <c r="C338">
         <v>66.307000000000002</v>
       </c>
       <c r="D338">
@@ -13357,7 +13428,7 @@
       <c r="J338">
         <v>1</v>
       </c>
-      <c r="K338" s="5">
+      <c r="K338" s="4">
         <v>66.307000000000002</v>
       </c>
     </row>
@@ -13368,7 +13439,7 @@
       <c r="B339" t="s">
         <v>16</v>
       </c>
-      <c r="C339" s="4">
+      <c r="C339">
         <v>66.366</v>
       </c>
       <c r="D339">
@@ -13392,7 +13463,7 @@
       <c r="J339">
         <v>1</v>
       </c>
-      <c r="K339" s="5">
+      <c r="K339" s="4">
         <v>66.366</v>
       </c>
     </row>
@@ -13403,7 +13474,7 @@
       <c r="B340" t="s">
         <v>128</v>
       </c>
-      <c r="C340" s="4">
+      <c r="C340">
         <v>66.402000000000001</v>
       </c>
       <c r="D340">
@@ -13427,7 +13498,7 @@
       <c r="J340">
         <v>1</v>
       </c>
-      <c r="K340" s="5">
+      <c r="K340" s="4">
         <v>66.402000000000001</v>
       </c>
     </row>
@@ -13438,7 +13509,7 @@
       <c r="B341" t="s">
         <v>33</v>
       </c>
-      <c r="C341" s="4">
+      <c r="C341">
         <v>66.453000000000017</v>
       </c>
       <c r="D341">
@@ -13462,7 +13533,7 @@
       <c r="J341">
         <v>1</v>
       </c>
-      <c r="K341" s="5">
+      <c r="K341" s="4">
         <v>66.453000000000017</v>
       </c>
     </row>
@@ -13473,7 +13544,7 @@
       <c r="B342" t="s">
         <v>34</v>
       </c>
-      <c r="C342" s="4">
+      <c r="C342">
         <v>67.277999999999992</v>
       </c>
       <c r="D342">
@@ -13497,7 +13568,7 @@
       <c r="J342">
         <v>1</v>
       </c>
-      <c r="K342" s="5">
+      <c r="K342" s="4">
         <v>67.277999999999992</v>
       </c>
     </row>
@@ -13508,7 +13579,7 @@
       <c r="B343" t="s">
         <v>10</v>
       </c>
-      <c r="C343" s="4">
+      <c r="C343">
         <v>67.697000000000003</v>
       </c>
       <c r="D343">
@@ -13532,7 +13603,7 @@
       <c r="J343">
         <v>1</v>
       </c>
-      <c r="K343" s="5">
+      <c r="K343" s="4">
         <v>67.697000000000003</v>
       </c>
     </row>
@@ -13543,7 +13614,7 @@
       <c r="B344" t="s">
         <v>18</v>
       </c>
-      <c r="C344" s="4">
+      <c r="C344">
         <v>67.722000000000008</v>
       </c>
       <c r="D344">
@@ -13567,7 +13638,7 @@
       <c r="J344">
         <v>1</v>
       </c>
-      <c r="K344" s="5">
+      <c r="K344" s="4">
         <v>67.722000000000008</v>
       </c>
     </row>
@@ -13578,7 +13649,7 @@
       <c r="B345" t="s">
         <v>120</v>
       </c>
-      <c r="C345" s="4">
+      <c r="C345">
         <v>68.35799999999999</v>
       </c>
       <c r="D345">
@@ -13602,7 +13673,7 @@
       <c r="J345">
         <v>1</v>
       </c>
-      <c r="K345" s="5">
+      <c r="K345" s="4">
         <v>68.35799999999999</v>
       </c>
     </row>
@@ -13613,7 +13684,7 @@
       <c r="B346" t="s">
         <v>14</v>
       </c>
-      <c r="C346" s="4">
+      <c r="C346">
         <v>69.101000000000013</v>
       </c>
       <c r="D346">
@@ -13637,7 +13708,7 @@
       <c r="J346">
         <v>1</v>
       </c>
-      <c r="K346" s="5">
+      <c r="K346" s="4">
         <v>69.101000000000013</v>
       </c>
     </row>
@@ -13648,7 +13719,7 @@
       <c r="B347" t="s">
         <v>21</v>
       </c>
-      <c r="C347" s="4">
+      <c r="C347">
         <v>69.461000000000013</v>
       </c>
       <c r="D347">
@@ -13672,7 +13743,7 @@
       <c r="J347">
         <v>1</v>
       </c>
-      <c r="K347" s="5">
+      <c r="K347" s="4">
         <v>69.461000000000013</v>
       </c>
     </row>
@@ -13683,7 +13754,7 @@
       <c r="B348" t="s">
         <v>76</v>
       </c>
-      <c r="C348" s="4">
+      <c r="C348">
         <v>70.171999999999997</v>
       </c>
       <c r="D348">
@@ -13707,7 +13778,7 @@
       <c r="J348">
         <v>1</v>
       </c>
-      <c r="K348" s="5">
+      <c r="K348" s="4">
         <v>70.171999999999997</v>
       </c>
     </row>
@@ -13718,7 +13789,7 @@
       <c r="B349" t="s">
         <v>67</v>
       </c>
-      <c r="C349" s="4">
+      <c r="C349">
         <v>70.948999999999998</v>
       </c>
       <c r="D349">
@@ -13742,7 +13813,7 @@
       <c r="J349">
         <v>1</v>
       </c>
-      <c r="K349" s="5">
+      <c r="K349" s="4">
         <v>70.948999999999998</v>
       </c>
     </row>
@@ -13753,7 +13824,7 @@
       <c r="B350" t="s">
         <v>18</v>
       </c>
-      <c r="C350" s="4">
+      <c r="C350">
         <v>71.702999999999989</v>
       </c>
       <c r="D350">
@@ -13777,7 +13848,7 @@
       <c r="J350">
         <v>1</v>
       </c>
-      <c r="K350" s="5">
+      <c r="K350" s="4">
         <v>71.702999999999989</v>
       </c>
     </row>
@@ -13788,7 +13859,7 @@
       <c r="B351" t="s">
         <v>6</v>
       </c>
-      <c r="C351" s="4">
+      <c r="C351">
         <v>77.292000000000002</v>
       </c>
       <c r="D351">
@@ -13812,7 +13883,7 @@
       <c r="J351">
         <v>1</v>
       </c>
-      <c r="K351" s="5">
+      <c r="K351" s="4">
         <v>77.292000000000002</v>
       </c>
     </row>
@@ -13823,7 +13894,7 @@
       <c r="B352" t="s">
         <v>21</v>
       </c>
-      <c r="C352" s="4">
+      <c r="C352">
         <v>63.341000000000008</v>
       </c>
       <c r="D352">
@@ -13847,7 +13918,7 @@
       <c r="J352">
         <v>1</v>
       </c>
-      <c r="K352" s="5">
+      <c r="K352" s="4">
         <v>63.341000000000008</v>
       </c>
     </row>
@@ -13858,7 +13929,7 @@
       <c r="B353" t="s">
         <v>14</v>
       </c>
-      <c r="C353" s="4">
+      <c r="C353">
         <v>64.765999999999991</v>
       </c>
       <c r="D353">
@@ -13882,7 +13953,7 @@
       <c r="J353">
         <v>1</v>
       </c>
-      <c r="K353" s="5">
+      <c r="K353" s="4">
         <v>64.765999999999991</v>
       </c>
     </row>
@@ -13893,7 +13964,7 @@
       <c r="B354" t="s">
         <v>57</v>
       </c>
-      <c r="C354" s="4">
+      <c r="C354">
         <v>65.346000000000004</v>
       </c>
       <c r="D354">
@@ -13917,7 +13988,7 @@
       <c r="J354">
         <v>1</v>
       </c>
-      <c r="K354" s="5">
+      <c r="K354" s="4">
         <v>65.346000000000004</v>
       </c>
     </row>
@@ -13928,7 +13999,7 @@
       <c r="B355" t="s">
         <v>23</v>
       </c>
-      <c r="C355" s="4">
+      <c r="C355">
         <v>65.51400000000001</v>
       </c>
       <c r="D355">
@@ -13952,7 +14023,7 @@
       <c r="J355">
         <v>1</v>
       </c>
-      <c r="K355" s="5">
+      <c r="K355" s="4">
         <v>65.51400000000001</v>
       </c>
     </row>
@@ -13963,7 +14034,7 @@
       <c r="B356" t="s">
         <v>8</v>
       </c>
-      <c r="C356" s="4">
+      <c r="C356">
         <v>67.501999999999995</v>
       </c>
       <c r="D356">
@@ -13987,7 +14058,7 @@
       <c r="J356">
         <v>1</v>
       </c>
-      <c r="K356" s="5">
+      <c r="K356" s="4">
         <v>67.501999999999995</v>
       </c>
     </row>
@@ -13998,7 +14069,7 @@
       <c r="B357" t="s">
         <v>16</v>
       </c>
-      <c r="C357" s="4">
+      <c r="C357">
         <v>67.77</v>
       </c>
       <c r="D357">
@@ -14022,7 +14093,7 @@
       <c r="J357">
         <v>1</v>
       </c>
-      <c r="K357" s="5">
+      <c r="K357" s="4">
         <v>67.77</v>
       </c>
     </row>
@@ -17349,6 +17420,671 @@
       </c>
       <c r="K452" s="1">
         <v>2.1843749999999999E-2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>369</v>
+      </c>
+      <c r="B453" t="s">
+        <v>57</v>
+      </c>
+      <c r="C453" s="3">
+        <v>5.6446999999999997E-2</v>
+      </c>
+      <c r="D453">
+        <v>1</v>
+      </c>
+      <c r="E453" t="s">
+        <v>379</v>
+      </c>
+      <c r="F453" t="s">
+        <v>194</v>
+      </c>
+      <c r="G453" t="s">
+        <v>37</v>
+      </c>
+      <c r="H453" t="s">
+        <v>36</v>
+      </c>
+      <c r="I453" t="s">
+        <v>381</v>
+      </c>
+      <c r="J453">
+        <v>1</v>
+      </c>
+      <c r="K453" s="3">
+        <v>5.6446999999999997E-2</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>370</v>
+      </c>
+      <c r="B454" t="s">
+        <v>33</v>
+      </c>
+      <c r="C454" s="3">
+        <v>5.6677999999999999E-2</v>
+      </c>
+      <c r="D454">
+        <v>2</v>
+      </c>
+      <c r="E454" t="s">
+        <v>379</v>
+      </c>
+      <c r="F454" t="s">
+        <v>194</v>
+      </c>
+      <c r="G454" t="s">
+        <v>37</v>
+      </c>
+      <c r="H454" t="s">
+        <v>36</v>
+      </c>
+      <c r="I454" t="s">
+        <v>381</v>
+      </c>
+      <c r="J454">
+        <v>1</v>
+      </c>
+      <c r="K454" s="3">
+        <v>5.6677999999999999E-2</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>371</v>
+      </c>
+      <c r="B455" t="s">
+        <v>14</v>
+      </c>
+      <c r="C455" s="3">
+        <v>5.8171E-2</v>
+      </c>
+      <c r="D455">
+        <v>3</v>
+      </c>
+      <c r="E455" t="s">
+        <v>379</v>
+      </c>
+      <c r="F455" t="s">
+        <v>194</v>
+      </c>
+      <c r="G455" t="s">
+        <v>37</v>
+      </c>
+      <c r="H455" t="s">
+        <v>36</v>
+      </c>
+      <c r="I455" t="s">
+        <v>381</v>
+      </c>
+      <c r="J455">
+        <v>1</v>
+      </c>
+      <c r="K455" s="3">
+        <v>5.8171E-2</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>372</v>
+      </c>
+      <c r="B456" t="s">
+        <v>10</v>
+      </c>
+      <c r="C456" s="3">
+        <v>5.9907000000000002E-2</v>
+      </c>
+      <c r="D456">
+        <v>4</v>
+      </c>
+      <c r="E456" t="s">
+        <v>379</v>
+      </c>
+      <c r="F456" t="s">
+        <v>194</v>
+      </c>
+      <c r="G456" t="s">
+        <v>37</v>
+      </c>
+      <c r="H456" t="s">
+        <v>36</v>
+      </c>
+      <c r="I456" t="s">
+        <v>381</v>
+      </c>
+      <c r="J456">
+        <v>1</v>
+      </c>
+      <c r="K456" s="3">
+        <v>5.9907000000000002E-2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>373</v>
+      </c>
+      <c r="B457" t="s">
+        <v>54</v>
+      </c>
+      <c r="C457" s="3">
+        <v>6.1447000000000002E-2</v>
+      </c>
+      <c r="D457">
+        <v>5</v>
+      </c>
+      <c r="E457" t="s">
+        <v>379</v>
+      </c>
+      <c r="F457" t="s">
+        <v>194</v>
+      </c>
+      <c r="G457" t="s">
+        <v>37</v>
+      </c>
+      <c r="H457" t="s">
+        <v>36</v>
+      </c>
+      <c r="I457" t="s">
+        <v>381</v>
+      </c>
+      <c r="J457">
+        <v>1</v>
+      </c>
+      <c r="K457" s="3">
+        <v>6.1447000000000002E-2</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>374</v>
+      </c>
+      <c r="B458" t="s">
+        <v>43</v>
+      </c>
+      <c r="C458" s="3">
+        <v>6.4756999999999995E-2</v>
+      </c>
+      <c r="D458">
+        <v>6</v>
+      </c>
+      <c r="E458" t="s">
+        <v>379</v>
+      </c>
+      <c r="F458" t="s">
+        <v>194</v>
+      </c>
+      <c r="G458" t="s">
+        <v>37</v>
+      </c>
+      <c r="H458" t="s">
+        <v>36</v>
+      </c>
+      <c r="I458" t="s">
+        <v>381</v>
+      </c>
+      <c r="J458">
+        <v>1</v>
+      </c>
+      <c r="K458" s="3">
+        <v>6.4756999999999995E-2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>375</v>
+      </c>
+      <c r="B459" t="s">
+        <v>8</v>
+      </c>
+      <c r="C459" s="3">
+        <v>6.6712999999999995E-2</v>
+      </c>
+      <c r="D459">
+        <v>7</v>
+      </c>
+      <c r="E459" t="s">
+        <v>379</v>
+      </c>
+      <c r="F459" t="s">
+        <v>194</v>
+      </c>
+      <c r="G459" t="s">
+        <v>37</v>
+      </c>
+      <c r="H459" t="s">
+        <v>36</v>
+      </c>
+      <c r="I459" t="s">
+        <v>381</v>
+      </c>
+      <c r="J459">
+        <v>1</v>
+      </c>
+      <c r="K459" s="3">
+        <v>6.6712999999999995E-2</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>376</v>
+      </c>
+      <c r="B460" t="s">
+        <v>30</v>
+      </c>
+      <c r="C460" s="3">
+        <v>7.1192000000000005E-2</v>
+      </c>
+      <c r="D460">
+        <v>8</v>
+      </c>
+      <c r="E460" t="s">
+        <v>379</v>
+      </c>
+      <c r="F460" t="s">
+        <v>194</v>
+      </c>
+      <c r="G460" t="s">
+        <v>37</v>
+      </c>
+      <c r="H460" t="s">
+        <v>36</v>
+      </c>
+      <c r="I460" t="s">
+        <v>381</v>
+      </c>
+      <c r="J460">
+        <v>1</v>
+      </c>
+      <c r="K460" s="3">
+        <v>7.1192000000000005E-2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>377</v>
+      </c>
+      <c r="B461" t="s">
+        <v>378</v>
+      </c>
+      <c r="C461" s="3">
+        <v>0.105104</v>
+      </c>
+      <c r="D461">
+        <v>9</v>
+      </c>
+      <c r="E461" t="s">
+        <v>379</v>
+      </c>
+      <c r="F461" t="s">
+        <v>194</v>
+      </c>
+      <c r="G461" t="s">
+        <v>37</v>
+      </c>
+      <c r="H461" t="s">
+        <v>36</v>
+      </c>
+      <c r="I461" t="s">
+        <v>381</v>
+      </c>
+      <c r="J461">
+        <v>1</v>
+      </c>
+      <c r="K461" s="3">
+        <v>0.105104</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>382</v>
+      </c>
+      <c r="B462" t="s">
+        <v>29</v>
+      </c>
+      <c r="C462" s="3">
+        <v>5.7303E-2</v>
+      </c>
+      <c r="D462">
+        <v>1</v>
+      </c>
+      <c r="E462" t="s">
+        <v>380</v>
+      </c>
+      <c r="F462" t="s">
+        <v>194</v>
+      </c>
+      <c r="G462" t="s">
+        <v>37</v>
+      </c>
+      <c r="H462" t="s">
+        <v>36</v>
+      </c>
+      <c r="I462" t="s">
+        <v>381</v>
+      </c>
+      <c r="J462">
+        <v>1</v>
+      </c>
+      <c r="K462" s="3">
+        <v>5.7303E-2</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>383</v>
+      </c>
+      <c r="B463" t="s">
+        <v>23</v>
+      </c>
+      <c r="C463" s="3">
+        <v>5.7361000000000002E-2</v>
+      </c>
+      <c r="D463">
+        <v>2</v>
+      </c>
+      <c r="E463" t="s">
+        <v>380</v>
+      </c>
+      <c r="F463" t="s">
+        <v>194</v>
+      </c>
+      <c r="G463" t="s">
+        <v>37</v>
+      </c>
+      <c r="H463" t="s">
+        <v>36</v>
+      </c>
+      <c r="I463" t="s">
+        <v>381</v>
+      </c>
+      <c r="J463">
+        <v>1</v>
+      </c>
+      <c r="K463" s="3">
+        <v>5.7361000000000002E-2</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>384</v>
+      </c>
+      <c r="B464" t="s">
+        <v>33</v>
+      </c>
+      <c r="C464" s="3">
+        <v>6.3645999999999994E-2</v>
+      </c>
+      <c r="D464">
+        <v>3</v>
+      </c>
+      <c r="E464" t="s">
+        <v>380</v>
+      </c>
+      <c r="F464" t="s">
+        <v>194</v>
+      </c>
+      <c r="G464" t="s">
+        <v>37</v>
+      </c>
+      <c r="H464" t="s">
+        <v>36</v>
+      </c>
+      <c r="I464" t="s">
+        <v>381</v>
+      </c>
+      <c r="J464">
+        <v>1</v>
+      </c>
+      <c r="K464" s="3">
+        <v>6.3645999999999994E-2</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>385</v>
+      </c>
+      <c r="B465" t="s">
+        <v>14</v>
+      </c>
+      <c r="C465" s="3">
+        <v>6.8575999999999998E-2</v>
+      </c>
+      <c r="D465">
+        <v>4</v>
+      </c>
+      <c r="E465" t="s">
+        <v>380</v>
+      </c>
+      <c r="F465" t="s">
+        <v>194</v>
+      </c>
+      <c r="G465" t="s">
+        <v>37</v>
+      </c>
+      <c r="H465" t="s">
+        <v>36</v>
+      </c>
+      <c r="I465" t="s">
+        <v>381</v>
+      </c>
+      <c r="J465">
+        <v>1</v>
+      </c>
+      <c r="K465" s="3">
+        <v>6.8575999999999998E-2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>386</v>
+      </c>
+      <c r="B466" t="s">
+        <v>81</v>
+      </c>
+      <c r="C466" s="3">
+        <v>6.8599999999999994E-2</v>
+      </c>
+      <c r="D466">
+        <v>5</v>
+      </c>
+      <c r="E466" t="s">
+        <v>380</v>
+      </c>
+      <c r="F466" t="s">
+        <v>194</v>
+      </c>
+      <c r="G466" t="s">
+        <v>37</v>
+      </c>
+      <c r="H466" t="s">
+        <v>36</v>
+      </c>
+      <c r="I466" t="s">
+        <v>381</v>
+      </c>
+      <c r="J466">
+        <v>1</v>
+      </c>
+      <c r="K466" s="3">
+        <v>6.8599999999999994E-2</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>387</v>
+      </c>
+      <c r="B467" t="s">
+        <v>76</v>
+      </c>
+      <c r="C467" s="3">
+        <v>6.9236000000000006E-2</v>
+      </c>
+      <c r="D467">
+        <v>6</v>
+      </c>
+      <c r="E467" t="s">
+        <v>380</v>
+      </c>
+      <c r="F467" t="s">
+        <v>194</v>
+      </c>
+      <c r="G467" t="s">
+        <v>37</v>
+      </c>
+      <c r="H467" t="s">
+        <v>36</v>
+      </c>
+      <c r="I467" t="s">
+        <v>381</v>
+      </c>
+      <c r="J467">
+        <v>1</v>
+      </c>
+      <c r="K467" s="3">
+        <v>6.9236000000000006E-2</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>388</v>
+      </c>
+      <c r="B468" t="s">
+        <v>35</v>
+      </c>
+      <c r="C468" s="3">
+        <v>6.9248000000000004E-2</v>
+      </c>
+      <c r="D468">
+        <v>7</v>
+      </c>
+      <c r="E468" t="s">
+        <v>380</v>
+      </c>
+      <c r="F468" t="s">
+        <v>194</v>
+      </c>
+      <c r="G468" t="s">
+        <v>37</v>
+      </c>
+      <c r="H468" t="s">
+        <v>36</v>
+      </c>
+      <c r="I468" t="s">
+        <v>381</v>
+      </c>
+      <c r="J468">
+        <v>1</v>
+      </c>
+      <c r="K468" s="3">
+        <v>6.9248000000000004E-2</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>389</v>
+      </c>
+      <c r="B469" t="s">
+        <v>392</v>
+      </c>
+      <c r="C469" s="3">
+        <v>7.2152999999999995E-2</v>
+      </c>
+      <c r="D469">
+        <v>8</v>
+      </c>
+      <c r="E469" t="s">
+        <v>380</v>
+      </c>
+      <c r="F469" t="s">
+        <v>194</v>
+      </c>
+      <c r="G469" t="s">
+        <v>37</v>
+      </c>
+      <c r="H469" t="s">
+        <v>36</v>
+      </c>
+      <c r="I469" t="s">
+        <v>381</v>
+      </c>
+      <c r="J469">
+        <v>1</v>
+      </c>
+      <c r="K469" s="3">
+        <v>7.2152999999999995E-2</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>390</v>
+      </c>
+      <c r="B470" t="s">
+        <v>33</v>
+      </c>
+      <c r="C470" s="3">
+        <v>7.5138999999999997E-2</v>
+      </c>
+      <c r="D470">
+        <v>9</v>
+      </c>
+      <c r="E470" t="s">
+        <v>380</v>
+      </c>
+      <c r="F470" t="s">
+        <v>194</v>
+      </c>
+      <c r="G470" t="s">
+        <v>37</v>
+      </c>
+      <c r="H470" t="s">
+        <v>36</v>
+      </c>
+      <c r="I470" t="s">
+        <v>381</v>
+      </c>
+      <c r="J470">
+        <v>1</v>
+      </c>
+      <c r="K470" s="3">
+        <v>7.5138999999999997E-2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>391</v>
+      </c>
+      <c r="B471" t="s">
+        <v>43</v>
+      </c>
+      <c r="C471" s="3">
+        <v>8.5787000000000002E-2</v>
+      </c>
+      <c r="D471">
+        <v>10</v>
+      </c>
+      <c r="E471" t="s">
+        <v>380</v>
+      </c>
+      <c r="F471" t="s">
+        <v>194</v>
+      </c>
+      <c r="G471" t="s">
+        <v>37</v>
+      </c>
+      <c r="H471" t="s">
+        <v>36</v>
+      </c>
+      <c r="I471" t="s">
+        <v>381</v>
+      </c>
+      <c r="J471">
+        <v>1</v>
+      </c>
+      <c r="K471" s="3">
+        <v>8.5787000000000002E-2</v>
       </c>
     </row>
   </sheetData>
